--- a/mlb/predictions/results_log.xlsx
+++ b/mlb/predictions/results_log.xlsx
@@ -631,7 +631,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H120"/>
+  <dimension ref="A1:H165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Bankroll: EUR 618.96    |    P&amp;L: +EUR 118.96    |    ROI: +12.5%    |    Win Rate: 53.3%  (32W / 28L)    |    Total Bets: 60</t>
+          <t>Bankroll: EUR 586.82    |    P&amp;L: +EUR 86.82    |    ROI: +6.4%    |    Win Rate: 50.0%  (42W / 42L)    |    Total Bets: 84</t>
         </is>
       </c>
     </row>
@@ -4284,43 +4284,1497 @@
       <c r="G118" s="24" t="n"/>
       <c r="H118" s="24" t="n"/>
     </row>
-    <row r="119" ht="15" customHeight="1">
-      <c r="A119" s="35" t="inlineStr">
+    <row r="119" ht="16" customHeight="1">
+      <c r="A119" s="27" t="inlineStr">
+        <is>
+          <t>Tue 21 Apr 2026</t>
+        </is>
+      </c>
+      <c r="B119" s="28" t="n">
+        <v>12</v>
+      </c>
+      <c r="C119" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="D119" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="E119" s="28" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="F119" s="29" t="n">
+        <v>174</v>
+      </c>
+      <c r="G119" s="30" t="n">
+        <v>94.02</v>
+      </c>
+      <c r="H119" s="29" t="n">
+        <v>712.98</v>
+      </c>
+    </row>
+    <row r="120" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A120" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Game</t>
+        </is>
+      </c>
+      <c r="B120" s="12" t="inlineStr">
+        <is>
+          <t>Pick</t>
+        </is>
+      </c>
+      <c r="C120" s="12" t="inlineStr">
+        <is>
+          <t>Odds</t>
+        </is>
+      </c>
+      <c r="D120" s="12" t="inlineStr">
+        <is>
+          <t>Stake (EUR)</t>
+        </is>
+      </c>
+      <c r="E120" s="12" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="F120" s="12" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="G120" s="12" t="inlineStr">
+        <is>
+          <t>P&amp;L (EUR)</t>
+        </is>
+      </c>
+      <c r="H120" s="12" t="inlineStr">
+        <is>
+          <t>Bankroll (EUR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A121" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  HOU @ CLE</t>
+        </is>
+      </c>
+      <c r="B121" s="24" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="C121" s="24" t="n"/>
+      <c r="D121" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="24" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F121" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G121" s="24" t="n"/>
+      <c r="H121" s="24" t="n"/>
+    </row>
+    <row r="122" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A122" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CIN @ TB</t>
+        </is>
+      </c>
+      <c r="B122" s="19" t="inlineStr">
+        <is>
+          <t>CIN -2.5</t>
+        </is>
+      </c>
+      <c r="C122" s="20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D122" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="E122" s="19" t="inlineStr">
+        <is>
+          <t>BET</t>
+        </is>
+      </c>
+      <c r="F122" s="22" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="G122" s="21" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="H122" s="21" t="n">
+        <v>633.36</v>
+      </c>
+    </row>
+    <row r="123" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A123" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  STL @ MIA</t>
+        </is>
+      </c>
+      <c r="B123" s="14" t="inlineStr">
+        <is>
+          <t>MIA -1.5</t>
+        </is>
+      </c>
+      <c r="C123" s="15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="D123" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="E123" s="14" t="inlineStr">
+        <is>
+          <t>BET</t>
+        </is>
+      </c>
+      <c r="F123" s="17" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="G123" s="16" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H123" s="16" t="n">
+        <v>627.36</v>
+      </c>
+    </row>
+    <row r="124" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A124" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  MIL @ DET</t>
+        </is>
+      </c>
+      <c r="B124" s="19" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="C124" s="20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="D124" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="E124" s="19" t="inlineStr">
+        <is>
+          <t>BET</t>
+        </is>
+      </c>
+      <c r="F124" s="22" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="G124" s="21" t="n">
+        <v>17.29</v>
+      </c>
+      <c r="H124" s="21" t="n">
+        <v>644.65</v>
+      </c>
+    </row>
+    <row r="125" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A125" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ATL @ WSH</t>
+        </is>
+      </c>
+      <c r="B125" s="24" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="C125" s="24" t="n"/>
+      <c r="D125" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="24" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F125" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G125" s="24" t="n"/>
+      <c r="H125" s="24" t="n"/>
+    </row>
+    <row r="126" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A126" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NYY @ BOS</t>
+        </is>
+      </c>
+      <c r="B126" s="19" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="C126" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D126" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="E126" s="19" t="inlineStr">
+        <is>
+          <t>BET</t>
+        </is>
+      </c>
+      <c r="F126" s="22" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="G126" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="H126" s="21" t="n">
+        <v>663.65</v>
+      </c>
+    </row>
+    <row r="127" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A127" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  MIN @ NYM</t>
+        </is>
+      </c>
+      <c r="B127" s="19" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="C127" s="20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D127" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="E127" s="19" t="inlineStr">
+        <is>
+          <t>BET</t>
+        </is>
+      </c>
+      <c r="F127" s="22" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="G127" s="21" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="H127" s="21" t="n">
+        <v>696.15</v>
+      </c>
+    </row>
+    <row r="128" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A128" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  BAL @ KC</t>
+        </is>
+      </c>
+      <c r="B128" s="14" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="C128" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D128" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="E128" s="14" t="inlineStr">
+        <is>
+          <t>BET</t>
+        </is>
+      </c>
+      <c r="F128" s="17" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="G128" s="16" t="n">
+        <v>-12</v>
+      </c>
+      <c r="H128" s="16" t="n">
+        <v>684.15</v>
+      </c>
+    </row>
+    <row r="129" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A129" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PHI @ CHC</t>
+        </is>
+      </c>
+      <c r="B129" s="14" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="C129" s="15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="D129" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="E129" s="14" t="inlineStr">
+        <is>
+          <t>BET</t>
+        </is>
+      </c>
+      <c r="F129" s="17" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="G129" s="16" t="n">
+        <v>-19</v>
+      </c>
+      <c r="H129" s="16" t="n">
+        <v>665.15</v>
+      </c>
+    </row>
+    <row r="130" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A130" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PIT @ TEX</t>
+        </is>
+      </c>
+      <c r="B130" s="14" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="C130" s="15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="D130" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="E130" s="14" t="inlineStr">
+        <is>
+          <t>BET</t>
+        </is>
+      </c>
+      <c r="F130" s="17" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="G130" s="16" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H130" s="16" t="n">
+        <v>659.15</v>
+      </c>
+    </row>
+    <row r="131" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A131" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SD @ COL</t>
+        </is>
+      </c>
+      <c r="B131" s="19" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="C131" s="20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="D131" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="E131" s="19" t="inlineStr">
+        <is>
+          <t>BET</t>
+        </is>
+      </c>
+      <c r="F131" s="22" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="G131" s="21" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="H131" s="21" t="n">
+        <v>667.1900000000001</v>
+      </c>
+    </row>
+    <row r="132" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A132" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TOR @ LAA</t>
+        </is>
+      </c>
+      <c r="B132" s="19" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="C132" s="20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="D132" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="E132" s="19" t="inlineStr">
+        <is>
+          <t>BET</t>
+        </is>
+      </c>
+      <c r="F132" s="22" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="G132" s="21" t="n">
+        <v>17.29</v>
+      </c>
+      <c r="H132" s="21" t="n">
+        <v>684.48</v>
+      </c>
+    </row>
+    <row r="133" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A133" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ATH @ SEA</t>
+        </is>
+      </c>
+      <c r="B133" s="19" t="inlineStr">
+        <is>
+          <t>ATH</t>
+        </is>
+      </c>
+      <c r="C133" s="20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="D133" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="E133" s="19" t="inlineStr">
+        <is>
+          <t>BET</t>
+        </is>
+      </c>
+      <c r="F133" s="22" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="G133" s="21" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="H133" s="21" t="n">
+        <v>718.98</v>
+      </c>
+    </row>
+    <row r="134" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A134" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CWS @ AZ</t>
+        </is>
+      </c>
+      <c r="B134" s="24" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="C134" s="25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="D134" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" s="24" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F134" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G134" s="24" t="n"/>
+      <c r="H134" s="24" t="n"/>
+    </row>
+    <row r="135" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A135" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  LAD @ SF</t>
+        </is>
+      </c>
+      <c r="B135" s="14" t="inlineStr">
+        <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="C135" s="15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="D135" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="E135" s="14" t="inlineStr">
+        <is>
+          <t>BET</t>
+        </is>
+      </c>
+      <c r="F135" s="17" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="G135" s="16" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H135" s="16" t="n">
+        <v>712.98</v>
+      </c>
+    </row>
+    <row r="136" ht="16" customHeight="1">
+      <c r="A136" s="7" t="inlineStr">
+        <is>
+          <t>Wed 22 Apr 2026</t>
+        </is>
+      </c>
+      <c r="B136" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C136" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D136" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E136" s="8" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="F136" s="9" t="n">
+        <v>99</v>
+      </c>
+      <c r="G136" s="10" t="n">
+        <v>-56.16</v>
+      </c>
+      <c r="H136" s="9" t="n">
+        <v>656.8200000000001</v>
+      </c>
+    </row>
+    <row r="137" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A137" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Game</t>
+        </is>
+      </c>
+      <c r="B137" s="12" t="inlineStr">
+        <is>
+          <t>Pick</t>
+        </is>
+      </c>
+      <c r="C137" s="12" t="inlineStr">
+        <is>
+          <t>Odds</t>
+        </is>
+      </c>
+      <c r="D137" s="12" t="inlineStr">
+        <is>
+          <t>Stake (EUR)</t>
+        </is>
+      </c>
+      <c r="E137" s="12" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="F137" s="12" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="G137" s="12" t="inlineStr">
+        <is>
+          <t>P&amp;L (EUR)</t>
+        </is>
+      </c>
+      <c r="H137" s="12" t="inlineStr">
+        <is>
+          <t>Bankroll (EUR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A138" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  STL @ MIA</t>
+        </is>
+      </c>
+      <c r="B138" s="24" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="C138" s="24" t="n"/>
+      <c r="D138" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" s="24" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F138" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G138" s="24" t="n"/>
+      <c r="H138" s="24" t="n"/>
+    </row>
+    <row r="139" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A139" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  HOU @ CLE</t>
+        </is>
+      </c>
+      <c r="B139" s="24" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="C139" s="24" t="n"/>
+      <c r="D139" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" s="24" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F139" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G139" s="24" t="n"/>
+      <c r="H139" s="24" t="n"/>
+    </row>
+    <row r="140" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A140" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CIN @ TB</t>
+        </is>
+      </c>
+      <c r="B140" s="24" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="C140" s="24" t="n"/>
+      <c r="D140" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" s="24" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F140" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G140" s="24" t="n"/>
+      <c r="H140" s="24" t="n"/>
+    </row>
+    <row r="141" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A141" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  BAL @ KC</t>
+        </is>
+      </c>
+      <c r="B141" s="24" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="C141" s="24" t="n"/>
+      <c r="D141" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" s="24" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F141" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G141" s="24" t="n"/>
+      <c r="H141" s="24" t="n"/>
+    </row>
+    <row r="142" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A142" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TOR @ LAA</t>
+        </is>
+      </c>
+      <c r="B142" s="14" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="C142" s="15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="D142" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="E142" s="14" t="inlineStr">
+        <is>
+          <t>BET</t>
+        </is>
+      </c>
+      <c r="F142" s="17" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="G142" s="16" t="n">
+        <v>-14</v>
+      </c>
+      <c r="H142" s="16" t="n">
+        <v>698.98</v>
+      </c>
+    </row>
+    <row r="143" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A143" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ATH @ SEA</t>
+        </is>
+      </c>
+      <c r="B143" s="14" t="inlineStr">
+        <is>
+          <t>ATH</t>
+        </is>
+      </c>
+      <c r="C143" s="15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D143" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="E143" s="14" t="inlineStr">
+        <is>
+          <t>BET</t>
+        </is>
+      </c>
+      <c r="F143" s="17" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="G143" s="16" t="n">
+        <v>-21</v>
+      </c>
+      <c r="H143" s="16" t="n">
+        <v>677.98</v>
+      </c>
+    </row>
+    <row r="144" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A144" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  MIL @ DET</t>
+        </is>
+      </c>
+      <c r="B144" s="14" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="C144" s="15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D144" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="E144" s="14" t="inlineStr">
+        <is>
+          <t>BET</t>
+        </is>
+      </c>
+      <c r="F144" s="17" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="G144" s="16" t="n">
+        <v>-14</v>
+      </c>
+      <c r="H144" s="16" t="n">
+        <v>663.98</v>
+      </c>
+    </row>
+    <row r="145" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A145" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ATL @ WSH</t>
+        </is>
+      </c>
+      <c r="B145" s="24" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="C145" s="24" t="n"/>
+      <c r="D145" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" s="24" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F145" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G145" s="24" t="n"/>
+      <c r="H145" s="24" t="n"/>
+    </row>
+    <row r="146" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A146" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NYY @ BOS</t>
+        </is>
+      </c>
+      <c r="B146" s="19" t="inlineStr">
+        <is>
+          <t>NYY -1.5</t>
+        </is>
+      </c>
+      <c r="C146" s="20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D146" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="E146" s="19" t="inlineStr">
+        <is>
+          <t>BET</t>
+        </is>
+      </c>
+      <c r="F146" s="22" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="G146" s="21" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H146" s="21" t="n">
+        <v>673.08</v>
+      </c>
+    </row>
+    <row r="147" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A147" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  MIN @ NYM</t>
+        </is>
+      </c>
+      <c r="B147" s="24" t="inlineStr">
+        <is>
+          <t>NYM</t>
+        </is>
+      </c>
+      <c r="C147" s="25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="D147" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E147" s="24" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F147" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G147" s="24" t="n"/>
+      <c r="H147" s="24" t="n"/>
+    </row>
+    <row r="148" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A148" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PHI @ CHC</t>
+        </is>
+      </c>
+      <c r="B148" s="14" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="C148" s="15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D148" s="16" t="n">
+        <v>29</v>
+      </c>
+      <c r="E148" s="14" t="inlineStr">
+        <is>
+          <t>BET</t>
+        </is>
+      </c>
+      <c r="F148" s="17" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="G148" s="16" t="n">
+        <v>-29</v>
+      </c>
+      <c r="H148" s="16" t="n">
+        <v>644.08</v>
+      </c>
+    </row>
+    <row r="149" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A149" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PIT @ TEX</t>
+        </is>
+      </c>
+      <c r="B149" s="19" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="C149" s="20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="D149" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="E149" s="19" t="inlineStr">
+        <is>
+          <t>BET</t>
+        </is>
+      </c>
+      <c r="F149" s="22" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="G149" s="21" t="n">
+        <v>12.74</v>
+      </c>
+      <c r="H149" s="21" t="n">
+        <v>656.8200000000001</v>
+      </c>
+    </row>
+    <row r="150" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A150" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SD @ COL</t>
+        </is>
+      </c>
+      <c r="B150" s="24" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="C150" s="25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="D150" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E150" s="24" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F150" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G150" s="24" t="n"/>
+      <c r="H150" s="24" t="n"/>
+    </row>
+    <row r="151" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A151" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CWS @ AZ</t>
+        </is>
+      </c>
+      <c r="B151" s="24" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="C151" s="25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="D151" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E151" s="24" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F151" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G151" s="24" t="n"/>
+      <c r="H151" s="24" t="n"/>
+    </row>
+    <row r="152" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A152" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  LAD @ SF</t>
+        </is>
+      </c>
+      <c r="B152" s="24" t="inlineStr"/>
+      <c r="C152" s="24" t="n"/>
+      <c r="D152" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E152" s="24" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F152" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G152" s="24" t="n"/>
+      <c r="H152" s="24" t="n"/>
+    </row>
+    <row r="153" ht="16" customHeight="1">
+      <c r="A153" s="7" t="inlineStr">
+        <is>
+          <t>Thu 23 Apr 2026</t>
+        </is>
+      </c>
+      <c r="B153" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C153" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D153" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E153" s="8" t="inlineStr">
+        <is>
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="F153" s="9" t="n">
+        <v>125</v>
+      </c>
+      <c r="G153" s="10" t="n">
+        <v>-70</v>
+      </c>
+      <c r="H153" s="9" t="n">
+        <v>586.8200000000001</v>
+      </c>
+    </row>
+    <row r="154" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A154" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Game</t>
+        </is>
+      </c>
+      <c r="B154" s="12" t="inlineStr">
+        <is>
+          <t>Pick</t>
+        </is>
+      </c>
+      <c r="C154" s="12" t="inlineStr">
+        <is>
+          <t>Odds</t>
+        </is>
+      </c>
+      <c r="D154" s="12" t="inlineStr">
+        <is>
+          <t>Stake (EUR)</t>
+        </is>
+      </c>
+      <c r="E154" s="12" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="F154" s="12" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="G154" s="12" t="inlineStr">
+        <is>
+          <t>P&amp;L (EUR)</t>
+        </is>
+      </c>
+      <c r="H154" s="12" t="inlineStr">
+        <is>
+          <t>Bankroll (EUR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A155" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ATL @ WSH</t>
+        </is>
+      </c>
+      <c r="B155" s="24" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="C155" s="24" t="n"/>
+      <c r="D155" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E155" s="24" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F155" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G155" s="24" t="n"/>
+      <c r="H155" s="24" t="n"/>
+    </row>
+    <row r="156" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A156" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  MIL @ DET</t>
+        </is>
+      </c>
+      <c r="B156" s="14" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="C156" s="15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D156" s="16" t="n">
+        <v>33</v>
+      </c>
+      <c r="E156" s="14" t="inlineStr">
+        <is>
+          <t>BET</t>
+        </is>
+      </c>
+      <c r="F156" s="17" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="G156" s="16" t="n">
+        <v>-33</v>
+      </c>
+      <c r="H156" s="16" t="n">
+        <v>623.8200000000001</v>
+      </c>
+    </row>
+    <row r="157" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A157" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PHI @ CHC</t>
+        </is>
+      </c>
+      <c r="B157" s="14" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="C157" s="15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="D157" s="16" t="n">
+        <v>26</v>
+      </c>
+      <c r="E157" s="14" t="inlineStr">
+        <is>
+          <t>BET</t>
+        </is>
+      </c>
+      <c r="F157" s="17" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="G157" s="16" t="n">
+        <v>-26</v>
+      </c>
+      <c r="H157" s="16" t="n">
+        <v>597.8200000000001</v>
+      </c>
+    </row>
+    <row r="158" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A158" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SD @ COL</t>
+        </is>
+      </c>
+      <c r="B158" s="24" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="C158" s="25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="D158" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E158" s="24" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F158" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G158" s="24" t="n"/>
+      <c r="H158" s="24" t="n"/>
+    </row>
+    <row r="159" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A159" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CWS @ AZ</t>
+        </is>
+      </c>
+      <c r="B159" s="24" t="inlineStr"/>
+      <c r="C159" s="24" t="n"/>
+      <c r="D159" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E159" s="24" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F159" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G159" s="24" t="n"/>
+      <c r="H159" s="24" t="n"/>
+    </row>
+    <row r="160" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A160" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  LAD @ SF</t>
+        </is>
+      </c>
+      <c r="B160" s="19" t="inlineStr">
+        <is>
+          <t>LAD -2.5</t>
+        </is>
+      </c>
+      <c r="C160" s="20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="D160" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="E160" s="19" t="inlineStr">
+        <is>
+          <t>BET</t>
+        </is>
+      </c>
+      <c r="F160" s="22" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="G160" s="21" t="n">
+        <v>35</v>
+      </c>
+      <c r="H160" s="21" t="n">
+        <v>632.8200000000001</v>
+      </c>
+    </row>
+    <row r="161" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A161" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NYY @ BOS</t>
+        </is>
+      </c>
+      <c r="B161" s="14" t="inlineStr">
+        <is>
+          <t>NYY -2.5</t>
+        </is>
+      </c>
+      <c r="C161" s="15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D161" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E161" s="14" t="inlineStr">
+        <is>
+          <t>BET</t>
+        </is>
+      </c>
+      <c r="F161" s="17" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="G161" s="16" t="n">
+        <v>-20</v>
+      </c>
+      <c r="H161" s="16" t="n">
+        <v>612.8200000000001</v>
+      </c>
+    </row>
+    <row r="162" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A162" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  MIN @ NYM</t>
+        </is>
+      </c>
+      <c r="B162" s="14" t="inlineStr">
+        <is>
+          <t>MIN -1.5</t>
+        </is>
+      </c>
+      <c r="C162" s="15" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="D162" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="E162" s="14" t="inlineStr">
+        <is>
+          <t>BET</t>
+        </is>
+      </c>
+      <c r="F162" s="17" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="G162" s="16" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H162" s="16" t="n">
+        <v>599.8200000000001</v>
+      </c>
+    </row>
+    <row r="163" outlineLevel="1" ht="13" customHeight="1">
+      <c r="A163" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PIT @ TEX</t>
+        </is>
+      </c>
+      <c r="B163" s="14" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="C163" s="15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D163" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="E163" s="14" t="inlineStr">
+        <is>
+          <t>BET</t>
+        </is>
+      </c>
+      <c r="F163" s="17" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="G163" s="16" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H163" s="16" t="n">
+        <v>586.8200000000001</v>
+      </c>
+    </row>
+    <row r="164" ht="15" customHeight="1">
+      <c r="A164" s="35" t="inlineStr">
         <is>
           <t>Week 17 Total</t>
         </is>
       </c>
-      <c r="B119" s="36" t="n">
-        <v>5</v>
-      </c>
-      <c r="C119" s="36" t="n">
-        <v>3</v>
-      </c>
-      <c r="D119" s="36" t="n">
-        <v>2</v>
-      </c>
-      <c r="E119" s="36" t="inlineStr">
-        <is>
-          <t>60%</t>
-        </is>
-      </c>
-      <c r="F119" s="37" t="n">
-        <v>70</v>
-      </c>
-      <c r="G119" s="37" t="n">
-        <v>-23.52</v>
-      </c>
-      <c r="H119" s="36" t="inlineStr"/>
-    </row>
-    <row r="120" ht="4" customHeight="1">
-      <c r="A120" s="34" t="n"/>
-      <c r="B120" s="34" t="n"/>
-      <c r="C120" s="34" t="n"/>
-      <c r="D120" s="34" t="n"/>
-      <c r="E120" s="34" t="n"/>
-      <c r="F120" s="34" t="n"/>
-      <c r="G120" s="34" t="n"/>
-      <c r="H120" s="34" t="n"/>
+      <c r="B164" s="36" t="n">
+        <v>29</v>
+      </c>
+      <c r="C164" s="36" t="n">
+        <v>13</v>
+      </c>
+      <c r="D164" s="36" t="n">
+        <v>16</v>
+      </c>
+      <c r="E164" s="36" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="F164" s="37" t="n">
+        <v>468</v>
+      </c>
+      <c r="G164" s="37" t="n">
+        <v>-55.66</v>
+      </c>
+      <c r="H164" s="36" t="inlineStr"/>
+    </row>
+    <row r="165" ht="4" customHeight="1">
+      <c r="A165" s="34" t="n"/>
+      <c r="B165" s="34" t="n"/>
+      <c r="C165" s="34" t="n"/>
+      <c r="D165" s="34" t="n"/>
+      <c r="E165" s="34" t="n"/>
+      <c r="F165" s="34" t="n"/>
+      <c r="G165" s="34" t="n"/>
+      <c r="H165" s="34" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
